--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 02_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 02_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655CD88B-9B7D-4087-9765-B32DF8D3D3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84770916-0018-4316-A5E9-E70A272516D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -781,9 +781,6 @@
     <t>ĐL Dũng Thu</t>
   </si>
   <si>
-    <t>Đã trả (27/02/26)</t>
-  </si>
-  <si>
     <t>Mắt camera</t>
   </si>
   <si>
@@ -791,6 +788,9 @@
   </si>
   <si>
     <t>Chuyển qua tháng 03/2026</t>
+  </si>
+  <si>
+    <t>Đã trả 20 VNSH01 (27/02/26)</t>
   </si>
 </sst>
 </file>
@@ -1081,6 +1081,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1088,9 +1091,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1581,18 +1581,18 @@
       </c>
       <c r="E3" s="3">
         <f>Xuất!AH4+Huỷ!AH3</f>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3">
         <f>C3+D3-E3</f>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1612,18 +1612,18 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="G4" s="4">
         <v>16</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2178,7 +2178,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3">
@@ -2214,11 +2214,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3286,7 +3286,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -3569,14 +3569,16 @@
       <c r="AB4" s="5">
         <v>3</v>
       </c>
-      <c r="AC4" s="5"/>
+      <c r="AC4" s="5">
+        <v>20</v>
+      </c>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
       <c r="AF4" s="5"/>
       <c r="AG4" s="5"/>
       <c r="AH4" s="5">
         <f>SUM(C4:AG4)</f>
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -3634,12 +3636,14 @@
       <c r="Z5" s="5">
         <v>13</v>
       </c>
-      <c r="AA5" s="5"/>
+      <c r="AA5" s="5">
+        <v>30</v>
+      </c>
       <c r="AB5" s="5">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="AC5" s="5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
@@ -3647,7 +3651,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>216</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -4448,7 +4452,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -5542,7 +5546,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
+      <c r="A2" s="32">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -5559,7 +5563,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -5574,7 +5578,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -5589,7 +5593,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -5604,7 +5608,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+      <c r="A6" s="32">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -5621,7 +5625,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -5636,7 +5640,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
+      <c r="A8" s="32">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5653,7 +5657,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5668,7 +5672,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+      <c r="A10" s="32">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5685,7 +5689,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5700,7 +5704,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
+      <c r="A12" s="32">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5717,7 +5721,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5749,7 +5753,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="35">
+      <c r="A15" s="32">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5766,7 +5770,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5815,7 +5819,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
+      <c r="A19" s="32">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5832,7 +5836,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5847,7 +5851,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32">
+      <c r="A21" s="33">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5864,7 +5868,7 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="15" t="s">
         <v>65</v>
       </c>
@@ -5879,7 +5883,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5894,7 +5898,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32">
+      <c r="A24" s="33">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5911,7 +5915,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
@@ -5926,7 +5930,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5941,7 +5945,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="32">
+      <c r="A27" s="33">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5962,7 +5966,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5977,7 +5981,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32">
+      <c r="A29" s="33">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5988,7 +5992,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>70</v>
@@ -5996,7 +6000,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="15" t="s">
         <v>71</v>
       </c>
@@ -6011,7 +6015,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -6021,7 +6025,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G31" s="16"/>
     </row>
@@ -6041,7 +6045,7 @@
         <v>69</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -6204,23 +6208,23 @@
       </c>
       <c r="E50" s="17">
         <f>SUM(E2:E32)</f>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F7" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="11">
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6300,18 +6304,18 @@
       </c>
       <c r="E3" s="3">
         <f>SUM('Nhập xuất tồn'!E3)</f>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(C3+D3-E3)</f>
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>SUM(F3-G3)</f>
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6331,18 +6335,18 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="G4" s="4">
         <v>14</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>80</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6743,7 +6747,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3">
@@ -6782,11 +6786,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6794,7 +6798,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 02_2026.xlsx
+++ b/5. Other/Thiết bị kho gửi/2026/Kho gửi phòng SX-BH 02_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Thiết bị kho gửi\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84770916-0018-4316-A5E9-E70A272516D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304F7BC8-FD6E-41B0-B11D-36E1A9A1D83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhập xuất tồn" sheetId="1" r:id="rId1"/>
@@ -1081,9 +1081,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1091,6 +1088,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1612,18 +1612,18 @@
       </c>
       <c r="E4" s="3">
         <f>Xuất!AH5+Huỷ!AH4</f>
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F4" s="3">
         <f>C4+D4-E4</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G4" s="4">
         <v>16</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4:H22" si="0">F4-G4</f>
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2214,11 +2214,11 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F3:F23)</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="2"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H24" s="3">
         <f>SUM(H3:H23)</f>
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3341,7 +3341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AH24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="8" customWidth="1"/>
@@ -3640,7 +3640,7 @@
         <v>30</v>
       </c>
       <c r="AB5" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="5">
         <v>0</v>
@@ -3651,7 +3651,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5">
         <f t="shared" ref="AH5:AH18" si="0">SUM(C5:AG5)</f>
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -4490,6 +4490,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="K28" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="K29" s="8">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:AH1"/>
@@ -5546,7 +5556,7 @@
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+      <c r="A2" s="35">
         <v>46055</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -5563,7 +5573,7 @@
       <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="15" t="s">
         <v>40</v>
       </c>
@@ -5578,7 +5588,7 @@
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="15" t="s">
         <v>41</v>
       </c>
@@ -5593,7 +5603,7 @@
       <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="15" t="s">
         <v>42</v>
       </c>
@@ -5608,7 +5618,7 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="35">
         <v>46056</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -5625,7 +5635,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
@@ -5640,7 +5650,7 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="35">
         <v>46057</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -5657,7 +5667,7 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="15" t="s">
         <v>40</v>
       </c>
@@ -5672,7 +5682,7 @@
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="35">
         <v>46058</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5689,7 +5699,7 @@
       <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="15" t="s">
         <v>50</v>
       </c>
@@ -5704,7 +5714,7 @@
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="35">
         <v>46059</v>
       </c>
       <c r="B12" s="15" t="s">
@@ -5721,7 +5731,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="15" t="s">
         <v>51</v>
       </c>
@@ -5753,7 +5763,7 @@
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="35">
         <v>46062</v>
       </c>
       <c r="B15" s="15" t="s">
@@ -5770,7 +5780,7 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
@@ -5819,7 +5829,7 @@
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32">
+      <c r="A19" s="35">
         <v>46065</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -5836,7 +5846,7 @@
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="15" t="s">
         <v>50</v>
       </c>
@@ -5851,7 +5861,7 @@
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="33">
+      <c r="A21" s="32">
         <v>46076</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -5868,7 +5878,7 @@
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="15" t="s">
         <v>65</v>
       </c>
@@ -5883,7 +5893,7 @@
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="15" t="s">
         <v>67</v>
       </c>
@@ -5898,7 +5908,7 @@
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="33">
+      <c r="A24" s="32">
         <v>46077</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -5915,7 +5925,7 @@
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="15" t="s">
         <v>64</v>
       </c>
@@ -5930,7 +5940,7 @@
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="15" t="s">
         <v>14</v>
       </c>
@@ -5945,7 +5955,7 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="33">
+      <c r="A27" s="32">
         <v>46078</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5966,7 +5976,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="15" t="s">
         <v>50</v>
       </c>
@@ -5981,7 +5991,7 @@
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
+      <c r="A29" s="32">
         <v>46079</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -6000,7 +6010,7 @@
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="15" t="s">
         <v>71</v>
       </c>
@@ -6015,7 +6025,7 @@
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
+      <c r="A31" s="33"/>
       <c r="B31" s="15" t="s">
         <v>50</v>
       </c>
@@ -6214,17 +6224,17 @@
   </sheetData>
   <autoFilter ref="A1:F7" xr:uid="{171653DB-B967-4059-9CE3-FD13B7B63DBC}"/>
   <mergeCells count="11">
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A29:A31"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A29:A31"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:F1000">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6335,18 +6345,18 @@
       </c>
       <c r="E4" s="3">
         <f>SUM('Nhập xuất tồn'!E4)</f>
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(C4+D4-E4)</f>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G4" s="4">
         <v>14</v>
       </c>
       <c r="H4" s="3">
         <f>SUM(F4-G4)</f>
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6786,11 +6796,11 @@
       </c>
       <c r="E19" s="10">
         <f>SUM(E3:E17)</f>
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F3:F18)</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G19" s="11">
         <f>SUM(G3:G17)</f>
@@ -6798,7 +6808,7 @@
       </c>
       <c r="H19" s="10">
         <f>SUM(H3:H18)</f>
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
